--- a/Outputs/Scenarios/PtX_demand_BG_Hydrogen.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BG_Hydrogen.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0009103253911235636</v>
       </c>
       <c r="K16" t="n">
-        <v>0.003032360985244317</v>
+        <v>0.001913808322212921</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001010786995081439</v>
+        <v>0.002198088657235992</v>
       </c>
     </row>
     <row r="18">
@@ -1481,7 +1481,7 @@
         <v>1.311624796363922e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001010786995081439</v>
+        <v>0.0009420379959582826</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001347625912720067</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01618659193698974</v>
+        <v>0.01021581352220822</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.005395530645663249</v>
+        <v>0.01173328779427562</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>7.092767961684565e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.005395530645663249</v>
+        <v>0.005028551911832407</v>
       </c>
     </row>
     <row r="43">
